--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -2133,7 +2133,7 @@
         <v>137373637</v>
       </c>
       <c r="B15" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>137373642</v>
       </c>
       <c r="B16" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137373645</v>
       </c>
       <c r="B22" t="n">
-        <v>91669</v>
+        <v>91671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137373633</v>
       </c>
       <c r="B26" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>137373639</v>
       </c>
       <c r="B27" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137373643</v>
       </c>
       <c r="B28" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>137373649</v>
       </c>
       <c r="B29" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>137373650</v>
       </c>
       <c r="B30" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137373652</v>
       </c>
       <c r="B31" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>137373655</v>
       </c>
       <c r="B32" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137373631</v>
       </c>
       <c r="B33" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>137373630</v>
       </c>
       <c r="B46" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>137373653</v>
       </c>
       <c r="B47" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>137373636</v>
       </c>
       <c r="B98" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>137373629</v>
       </c>
       <c r="B101" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>137373634</v>
       </c>
       <c r="B4" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137373635</v>
       </c>
       <c r="B5" t="n">
-        <v>87465</v>
+        <v>87470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137373627</v>
       </c>
       <c r="B14" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>137373637</v>
       </c>
       <c r="B15" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>137373642</v>
       </c>
       <c r="B16" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137373645</v>
       </c>
       <c r="B22" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137373633</v>
       </c>
       <c r="B26" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>137373639</v>
       </c>
       <c r="B27" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137373643</v>
       </c>
       <c r="B28" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>137373649</v>
       </c>
       <c r="B29" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>137373650</v>
       </c>
       <c r="B30" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137373652</v>
       </c>
       <c r="B31" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>137373655</v>
       </c>
       <c r="B32" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137373631</v>
       </c>
       <c r="B33" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>137373630</v>
       </c>
       <c r="B46" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>137373653</v>
       </c>
       <c r="B47" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>137373636</v>
       </c>
       <c r="B98" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>137373629</v>
       </c>
       <c r="B101" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>137373638</v>
       </c>
       <c r="B123" t="n">
-        <v>87550</v>
+        <v>87555</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>137373657</v>
       </c>
       <c r="B124" t="n">
-        <v>87456</v>
+        <v>87461</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -5677,7 +5677,7 @@
         <v>137373630</v>
       </c>
       <c r="B46" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>137373634</v>
       </c>
       <c r="B4" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137373635</v>
       </c>
       <c r="B5" t="n">
-        <v>87470</v>
+        <v>87481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137373627</v>
       </c>
       <c r="B14" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>137373637</v>
       </c>
       <c r="B15" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>137373642</v>
       </c>
       <c r="B16" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>137373645</v>
       </c>
       <c r="B22" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>137373633</v>
       </c>
       <c r="B26" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>137373639</v>
       </c>
       <c r="B27" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137373643</v>
       </c>
       <c r="B28" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>137373649</v>
       </c>
       <c r="B29" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>137373650</v>
       </c>
       <c r="B30" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137373652</v>
       </c>
       <c r="B31" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>137373655</v>
       </c>
       <c r="B32" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137373631</v>
       </c>
       <c r="B33" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>137373630</v>
       </c>
       <c r="B46" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>137373653</v>
       </c>
       <c r="B47" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>137373636</v>
       </c>
       <c r="B98" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>137373629</v>
       </c>
       <c r="B101" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>137373638</v>
       </c>
       <c r="B123" t="n">
-        <v>87555</v>
+        <v>87566</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>137373657</v>
       </c>
       <c r="B124" t="n">
-        <v>87461</v>
+        <v>87472</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ124"/>
+  <dimension ref="A1:AZ125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,7 +913,7 @@
         <v>137373634</v>
       </c>
       <c r="B4" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137373635</v>
       </c>
       <c r="B5" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137373627</v>
       </c>
       <c r="B14" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137373637</v>
+        <v>137400918</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>87619</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>3739</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696776</v>
+        <v>696555</v>
       </c>
       <c r="R15" t="n">
-        <v>6643785</v>
+        <v>6643838</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2195,22 +2195,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,49 +2225,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373637</t>
+          <t>https://artportalen.se/Sighting/137400918</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137373642</v>
+        <v>137373637</v>
       </c>
       <c r="B16" t="n">
-        <v>93152</v>
+        <v>93494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696812</v>
+        <v>696776</v>
       </c>
       <c r="R16" t="n">
-        <v>6643787</v>
+        <v>6643785</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2348,16 +2348,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373642</t>
+          <t>https://artportalen.se/Sighting/137373637</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55545208</v>
+        <v>137373642</v>
       </c>
       <c r="B17" t="n">
-        <v>91966</v>
+        <v>93153</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,36 +2365,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5321</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696737</v>
+        <v>696812</v>
       </c>
       <c r="R17" t="n">
-        <v>6643878</v>
+        <v>6643787</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2421,17 +2419,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På asplåga. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,56 +2443,55 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545208</t>
+          <t>https://artportalen.se/Sighting/137373642</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55545398</v>
+        <v>55545208</v>
       </c>
       <c r="B18" t="n">
-        <v>91930</v>
+        <v>91966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>5321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696438</v>
+        <v>696737</v>
       </c>
       <c r="R18" t="n">
-        <v>6643716</v>
+        <v>6643878</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2541,7 +2543,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>På asplåga. Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2568,13 +2570,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545398</t>
+          <t>https://artportalen.se/Sighting/55545208</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55545399</v>
+        <v>55545398</v>
       </c>
       <c r="B19" t="n">
         <v>91930</v>
@@ -2602,16 +2604,8 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2619,10 +2613,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696470</v>
+        <v>696438</v>
       </c>
       <c r="R19" t="n">
-        <v>6643661</v>
+        <v>6643716</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2686,13 +2680,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545399</t>
+          <t>https://artportalen.se/Sighting/55545398</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55545434</v>
+        <v>55545399</v>
       </c>
       <c r="B20" t="n">
         <v>91930</v>
@@ -2720,8 +2714,16 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2729,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696973</v>
+        <v>696470</v>
       </c>
       <c r="R20" t="n">
-        <v>6643918</v>
+        <v>6643661</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2769,7 +2771,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,16 +2798,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545434</t>
+          <t>https://artportalen.se/Sighting/55545399</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830936</v>
+        <v>55545434</v>
       </c>
       <c r="B21" t="n">
-        <v>91995</v>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,19 +2833,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696871</v>
+        <v>696973</v>
       </c>
       <c r="R21" t="n">
-        <v>6643836</v>
+        <v>6643918</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2867,22 +2871,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på blockrik mark. Stort inslag av gammal rötskadad asp.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,71 +2890,72 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830936</t>
+          <t>https://artportalen.se/Sighting/55545434</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137373645</v>
+        <v>132830936</v>
       </c>
       <c r="B22" t="n">
-        <v>91688</v>
+        <v>91995</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5747</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696866</v>
+        <v>696871</v>
       </c>
       <c r="R22" t="n">
-        <v>6643805</v>
+        <v>6643836</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2979,22 +2979,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,64 +3009,62 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373645</t>
+          <t>https://artportalen.se/Sighting/132830936</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55545592</v>
+        <v>137373645</v>
       </c>
       <c r="B23" t="n">
-        <v>93233</v>
+        <v>91689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>697043</v>
+        <v>696866</v>
       </c>
       <c r="R23" t="n">
-        <v>6643847</v>
+        <v>6643805</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3093,17 +3091,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,31 +3115,30 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545592</t>
+          <t>https://artportalen.se/Sighting/137373645</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55545594</v>
+        <v>55545592</v>
       </c>
       <c r="B24" t="n">
         <v>93233</v>
@@ -3173,10 +3175,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>697030</v>
+        <v>697043</v>
       </c>
       <c r="R24" t="n">
-        <v>6643834</v>
+        <v>6643847</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3240,13 +3242,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545594</t>
+          <t>https://artportalen.se/Sighting/55545592</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55545704</v>
+        <v>55545594</v>
       </c>
       <c r="B25" t="n">
         <v>93233</v>
@@ -3283,10 +3285,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696975</v>
+        <v>697030</v>
       </c>
       <c r="R25" t="n">
-        <v>6643792</v>
+        <v>6643834</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3350,16 +3352,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545704</t>
+          <t>https://artportalen.se/Sighting/55545594</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137373633</v>
+        <v>55545704</v>
       </c>
       <c r="B26" t="n">
-        <v>93517</v>
+        <v>93233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3385,19 +3387,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696730</v>
+        <v>696975</v>
       </c>
       <c r="R26" t="n">
-        <v>6643674</v>
+        <v>6643792</v>
       </c>
       <c r="S26" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3421,22 +3425,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:26</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3445,33 +3444,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373633</t>
+          <t>https://artportalen.se/Sighting/55545704</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137373639</v>
+        <v>137373633</v>
       </c>
       <c r="B27" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3503,13 +3503,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>696767</v>
+        <v>696730</v>
       </c>
       <c r="R27" t="n">
-        <v>6643787</v>
+        <v>6643674</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,16 +3574,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373639</t>
+          <t>https://artportalen.se/Sighting/137373633</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137373643</v>
+        <v>137373639</v>
       </c>
       <c r="B28" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696816</v>
+        <v>696767</v>
       </c>
       <c r="R28" t="n">
-        <v>6643810</v>
+        <v>6643787</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,16 +3686,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373643</t>
+          <t>https://artportalen.se/Sighting/137373639</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137373649</v>
+        <v>137373643</v>
       </c>
       <c r="B29" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>697031</v>
+        <v>696816</v>
       </c>
       <c r="R29" t="n">
-        <v>6643872</v>
+        <v>6643810</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3798,16 +3798,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373649</t>
+          <t>https://artportalen.se/Sighting/137373643</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137373650</v>
+        <v>137373649</v>
       </c>
       <c r="B30" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>697031</v>
       </c>
       <c r="R30" t="n">
-        <v>6643874</v>
+        <v>6643872</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,16 +3910,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373650</t>
+          <t>https://artportalen.se/Sighting/137373649</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137373652</v>
+        <v>137373650</v>
       </c>
       <c r="B31" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>697073</v>
+        <v>697031</v>
       </c>
       <c r="R31" t="n">
-        <v>6643889</v>
+        <v>6643874</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4022,16 +4022,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373652</t>
+          <t>https://artportalen.se/Sighting/137373650</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137373655</v>
+        <v>137373652</v>
       </c>
       <c r="B32" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>697033</v>
+        <v>697073</v>
       </c>
       <c r="R32" t="n">
-        <v>6643905</v>
+        <v>6643889</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4134,16 +4134,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373655</t>
+          <t>https://artportalen.se/Sighting/137373652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137373631</v>
+        <v>137373655</v>
       </c>
       <c r="B33" t="n">
-        <v>93519</v>
+        <v>93518</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4151,21 +4151,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696613</v>
+        <v>697033</v>
       </c>
       <c r="R33" t="n">
-        <v>6643635</v>
+        <v>6643905</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4246,59 +4246,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373631</t>
+          <t>https://artportalen.se/Sighting/137373655</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132826336</v>
+        <v>137373631</v>
       </c>
       <c r="B34" t="n">
-        <v>57972</v>
+        <v>93520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696492</v>
+        <v>696613</v>
       </c>
       <c r="R34" t="n">
-        <v>6643764</v>
+        <v>6643635</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4322,22 +4317,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4352,24 +4347,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132826336</t>
+          <t>https://artportalen.se/Sighting/137373631</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132830911</v>
+        <v>132826336</v>
       </c>
       <c r="B35" t="n">
         <v>57972</v>
@@ -4405,14 +4400,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696479</v>
+        <v>696492</v>
       </c>
       <c r="R35" t="n">
-        <v>6643760</v>
+        <v>6643764</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4444,7 +4439,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4454,7 +4449,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,24 +4464,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830911</t>
+          <t>https://artportalen.se/Sighting/132826336</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132830947</v>
+        <v>132830911</v>
       </c>
       <c r="B36" t="n">
         <v>57972</v>
@@ -4517,19 +4512,19 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696785</v>
+        <v>696479</v>
       </c>
       <c r="R36" t="n">
-        <v>6643731</v>
+        <v>6643760</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4561,7 +4556,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4571,7 +4566,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4597,13 +4592,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830947</t>
+          <t>https://artportalen.se/Sighting/132830911</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132830963</v>
+        <v>132830947</v>
       </c>
       <c r="B37" t="n">
         <v>57972</v>
@@ -4634,7 +4629,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4643,10 +4638,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696701</v>
+        <v>696785</v>
       </c>
       <c r="R37" t="n">
-        <v>6643708</v>
+        <v>6643731</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4678,7 +4673,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4688,7 +4683,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4714,13 +4709,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830963</t>
+          <t>https://artportalen.se/Sighting/132830947</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132830971</v>
+        <v>132830963</v>
       </c>
       <c r="B38" t="n">
         <v>57972</v>
@@ -4751,7 +4746,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4760,10 +4755,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696622</v>
+        <v>696701</v>
       </c>
       <c r="R38" t="n">
-        <v>6643679</v>
+        <v>6643708</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4795,7 +4790,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4805,7 +4800,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4831,33 +4826,33 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830971</t>
+          <t>https://artportalen.se/Sighting/132830963</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132830978</v>
+        <v>132830971</v>
       </c>
       <c r="B39" t="n">
-        <v>58519</v>
+        <v>57972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4866,24 +4861,21 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696664</v>
+        <v>696622</v>
       </c>
       <c r="R39" t="n">
-        <v>6643658</v>
+        <v>6643679</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4915,7 +4907,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4925,7 +4917,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4951,33 +4943,33 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830978</t>
+          <t>https://artportalen.se/Sighting/132830971</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132830945</v>
+        <v>132830978</v>
       </c>
       <c r="B40" t="n">
-        <v>58349</v>
+        <v>58519</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5000,10 +4992,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>696784</v>
+        <v>696664</v>
       </c>
       <c r="R40" t="n">
-        <v>6643729</v>
+        <v>6643658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5035,7 +5027,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5045,7 +5037,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5071,13 +5063,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830945</t>
+          <t>https://artportalen.se/Sighting/132830978</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132830977</v>
+        <v>132830945</v>
       </c>
       <c r="B41" t="n">
         <v>58349</v>
@@ -5120,10 +5112,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>696664</v>
+        <v>696784</v>
       </c>
       <c r="R41" t="n">
-        <v>6643658</v>
+        <v>6643729</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5155,7 +5147,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5165,7 +5157,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5191,16 +5183,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830977</t>
+          <t>https://artportalen.se/Sighting/132830945</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132826159</v>
+        <v>132830977</v>
       </c>
       <c r="B42" t="n">
-        <v>58131</v>
+        <v>58349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5208,16 +5200,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103023</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5226,21 +5218,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>696520</v>
+        <v>696664</v>
       </c>
       <c r="R42" t="n">
-        <v>6643691</v>
+        <v>6643658</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5272,7 +5267,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5282,7 +5277,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5297,24 +5292,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132826159</t>
+          <t>https://artportalen.se/Sighting/132830977</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132830912</v>
+        <v>132826159</v>
       </c>
       <c r="B43" t="n">
         <v>58131</v>
@@ -5343,24 +5338,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>696459</v>
+        <v>696520</v>
       </c>
       <c r="R43" t="n">
-        <v>6643757</v>
+        <v>6643691</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5392,7 +5384,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5402,7 +5394,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5417,24 +5409,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830912</t>
+          <t>https://artportalen.se/Sighting/132826159</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132830972</v>
+        <v>132830912</v>
       </c>
       <c r="B44" t="n">
         <v>58131</v>
@@ -5473,14 +5465,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696637</v>
+        <v>696459</v>
       </c>
       <c r="R44" t="n">
-        <v>6643668</v>
+        <v>6643757</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5512,7 +5504,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5522,7 +5514,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5548,16 +5540,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830972</t>
+          <t>https://artportalen.se/Sighting/132830912</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132830964</v>
+        <v>132830972</v>
       </c>
       <c r="B45" t="n">
-        <v>58658</v>
+        <v>58131</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5565,16 +5557,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103044</v>
+        <v>103023</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5597,10 +5589,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>696700</v>
+        <v>696637</v>
       </c>
       <c r="R45" t="n">
-        <v>6643694</v>
+        <v>6643668</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5632,7 +5624,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5642,7 +5634,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5668,54 +5660,62 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830964</t>
+          <t>https://artportalen.se/Sighting/132830972</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137373630</v>
+        <v>132830964</v>
       </c>
       <c r="B46" t="n">
-        <v>111745</v>
+        <v>58658</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219711</v>
+        <v>103044</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>696640</v>
+        <v>696700</v>
       </c>
       <c r="R46" t="n">
-        <v>6643744</v>
+        <v>6643694</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5739,22 +5739,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5769,49 +5769,49 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373630</t>
+          <t>https://artportalen.se/Sighting/132830964</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137373653</v>
+        <v>137373630</v>
       </c>
       <c r="B47" t="n">
-        <v>99408</v>
+        <v>111746</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>697075</v>
+        <v>696640</v>
       </c>
       <c r="R47" t="n">
-        <v>6643893</v>
+        <v>6643744</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5892,16 +5892,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373653</t>
+          <t>https://artportalen.se/Sighting/137373630</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132830961</v>
+        <v>137373653</v>
       </c>
       <c r="B48" t="n">
-        <v>99230</v>
+        <v>99409</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5909,21 +5909,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219874</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5933,13 +5933,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>696729</v>
+        <v>697075</v>
       </c>
       <c r="R48" t="n">
-        <v>6643708</v>
+        <v>6643893</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5963,22 +5963,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5993,78 +5993,62 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830961</t>
+          <t>https://artportalen.se/Sighting/137373653</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122318142</v>
+        <v>132830961</v>
       </c>
       <c r="B49" t="n">
-        <v>99118</v>
+        <v>99230</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Naturbarrskog sydost om Edsbro , Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696790</v>
+        <v>696729</v>
       </c>
       <c r="R49" t="n">
-        <v>6643908</v>
+        <v>6643708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6091,12 +6075,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6105,7 +6099,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6123,13 +6116,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318142</t>
+          <t>https://artportalen.se/Sighting/132830961</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122318416</v>
+        <v>122318142</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6159,7 +6152,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6172,16 +6165,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Naturbarrskog sydost om Edsbro , Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>696765</v>
+        <v>696790</v>
       </c>
       <c r="R50" t="n">
-        <v>6643857</v>
+        <v>6643908</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6222,6 +6217,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6239,13 +6235,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318416</t>
+          <t>https://artportalen.se/Sighting/122318142</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122318564</v>
+        <v>122318416</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6275,7 +6271,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6294,10 +6290,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>696737</v>
+        <v>696765</v>
       </c>
       <c r="R51" t="n">
-        <v>6643788</v>
+        <v>6643857</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6355,13 +6351,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318564</t>
+          <t>https://artportalen.se/Sighting/122318416</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122318601</v>
+        <v>122318564</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6391,7 +6387,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6410,10 +6406,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>696750</v>
+        <v>696737</v>
       </c>
       <c r="R52" t="n">
-        <v>6643770</v>
+        <v>6643788</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6471,13 +6467,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318601</t>
+          <t>https://artportalen.se/Sighting/122318564</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122318667</v>
+        <v>122318601</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6507,7 +6503,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6526,10 +6522,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>696760</v>
+        <v>696750</v>
       </c>
       <c r="R53" t="n">
-        <v>6643790</v>
+        <v>6643770</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6587,13 +6583,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318667</t>
+          <t>https://artportalen.se/Sighting/122318601</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122318689</v>
+        <v>122318667</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6623,7 +6619,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6636,18 +6632,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>696765</v>
+        <v>696760</v>
       </c>
       <c r="R54" t="n">
-        <v>6643808</v>
+        <v>6643790</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6688,7 +6682,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6706,13 +6699,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318689</t>
+          <t>https://artportalen.se/Sighting/122318667</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122318788</v>
+        <v>122318689</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6742,7 +6735,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6755,16 +6748,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>696781</v>
+        <v>696765</v>
       </c>
       <c r="R55" t="n">
-        <v>6643831</v>
+        <v>6643808</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6805,6 +6800,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6822,13 +6818,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318788</t>
+          <t>https://artportalen.se/Sighting/122318689</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122318816</v>
+        <v>122318788</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6858,7 +6854,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6877,10 +6873,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>696780</v>
+        <v>696781</v>
       </c>
       <c r="R56" t="n">
-        <v>6643852</v>
+        <v>6643831</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6938,13 +6934,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318816</t>
+          <t>https://artportalen.se/Sighting/122318788</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122318880</v>
+        <v>122318816</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6974,7 +6970,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6993,10 +6989,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>696790</v>
+        <v>696780</v>
       </c>
       <c r="R57" t="n">
-        <v>6643862</v>
+        <v>6643852</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7054,13 +7050,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318880</t>
+          <t>https://artportalen.se/Sighting/122318816</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122318944</v>
+        <v>122318880</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7090,7 +7086,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7103,18 +7099,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>696821</v>
+        <v>696790</v>
       </c>
       <c r="R58" t="n">
-        <v>6643861</v>
+        <v>6643862</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7155,7 +7149,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7173,13 +7166,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318944</t>
+          <t>https://artportalen.se/Sighting/122318880</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122319229</v>
+        <v>122318944</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7209,7 +7202,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7222,16 +7215,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Eklund, Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>696950</v>
+        <v>696821</v>
       </c>
       <c r="R59" t="n">
-        <v>6643906</v>
+        <v>6643861</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7261,51 +7256,42 @@
           <t>2025-01-26</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-01-26</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122319229</t>
+          <t>https://artportalen.se/Sighting/122318944</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122319238</v>
+        <v>122319229</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7335,7 +7321,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7350,14 +7336,14 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Dammviken, Upl</t>
+          <t>Eklund, Eklund, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>696896</v>
+        <v>696950</v>
       </c>
       <c r="R60" t="n">
-        <v>6643891</v>
+        <v>6643906</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7387,9 +7373,19 @@
           <t>2025-01-26</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-01-26</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7404,24 +7400,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122319238</t>
+          <t>https://artportalen.se/Sighting/122319229</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122319284</v>
+        <v>122319238</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7451,7 +7447,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7466,14 +7462,14 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Dammviken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>696914</v>
+        <v>696896</v>
       </c>
       <c r="R61" t="n">
-        <v>6643869</v>
+        <v>6643891</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7531,13 +7527,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122319284</t>
+          <t>https://artportalen.se/Sighting/122319238</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122319349</v>
+        <v>122319284</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7567,7 +7563,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -7586,10 +7582,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>696877</v>
+        <v>696914</v>
       </c>
       <c r="R62" t="n">
-        <v>6643851</v>
+        <v>6643869</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7647,13 +7643,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122319349</t>
+          <t>https://artportalen.se/Sighting/122319284</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122319414</v>
+        <v>122319349</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -7683,7 +7679,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7698,14 +7694,14 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Eklund, Eklund, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>696867</v>
+        <v>696877</v>
       </c>
       <c r="R63" t="n">
-        <v>6643836</v>
+        <v>6643851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7735,19 +7731,9 @@
           <t>2025-01-26</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-01-26</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7762,24 +7748,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122319414</t>
+          <t>https://artportalen.se/Sighting/122319349</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122319573</v>
+        <v>122319414</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7809,7 +7795,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7828,10 +7814,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>696744</v>
+        <v>696867</v>
       </c>
       <c r="R64" t="n">
-        <v>6643779</v>
+        <v>6643836</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7863,7 +7849,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7873,7 +7859,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7899,13 +7885,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122319573</t>
+          <t>https://artportalen.se/Sighting/122319414</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122347695</v>
+        <v>122319573</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7935,7 +7921,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7954,10 +7940,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>696895</v>
+        <v>696744</v>
       </c>
       <c r="R65" t="n">
-        <v>6643837</v>
+        <v>6643779</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7989,7 +7975,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7999,7 +7985,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8025,16 +8011,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122347695</t>
+          <t>https://artportalen.se/Sighting/122319573</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132821365</v>
+        <v>122347695</v>
       </c>
       <c r="B66" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8061,7 +8047,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8069,16 +8055,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Eklund, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>696684</v>
+        <v>696895</v>
       </c>
       <c r="R66" t="n">
-        <v>6643670</v>
+        <v>6643837</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8105,22 +8096,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8140,19 +8131,19 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821365</t>
+          <t>https://artportalen.se/Sighting/122347695</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132821435</v>
+        <v>132821365</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -8182,7 +8173,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8196,10 +8187,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>696687</v>
+        <v>696684</v>
       </c>
       <c r="R67" t="n">
-        <v>6643684</v>
+        <v>6643670</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8231,7 +8222,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8241,7 +8232,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8267,13 +8258,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821435</t>
+          <t>https://artportalen.se/Sighting/132821365</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132821474</v>
+        <v>132821435</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -8303,7 +8294,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8317,10 +8308,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>696684</v>
+        <v>696687</v>
       </c>
       <c r="R68" t="n">
-        <v>6643683</v>
+        <v>6643684</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8352,7 +8343,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8362,7 +8353,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8388,13 +8379,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821474</t>
+          <t>https://artportalen.se/Sighting/132821435</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132821521</v>
+        <v>132821474</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -8424,7 +8415,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8438,10 +8429,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>696690</v>
+        <v>696684</v>
       </c>
       <c r="R69" t="n">
-        <v>6643690</v>
+        <v>6643683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8473,7 +8464,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8483,7 +8474,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8509,13 +8500,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821521</t>
+          <t>https://artportalen.se/Sighting/132821474</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132821594</v>
+        <v>132821521</v>
       </c>
       <c r="B70" t="n">
         <v>99195</v>
@@ -8545,7 +8536,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8559,10 +8550,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>696683</v>
+        <v>696690</v>
       </c>
       <c r="R70" t="n">
-        <v>6643725</v>
+        <v>6643690</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8594,7 +8585,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8604,7 +8595,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8630,13 +8621,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821594</t>
+          <t>https://artportalen.se/Sighting/132821521</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132821661</v>
+        <v>132821594</v>
       </c>
       <c r="B71" t="n">
         <v>99195</v>
@@ -8664,7 +8655,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -8676,10 +8671,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>696690</v>
+        <v>696683</v>
       </c>
       <c r="R71" t="n">
-        <v>6643717</v>
+        <v>6643725</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8711,7 +8706,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8721,7 +8716,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8741,19 +8736,19 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821661</t>
+          <t>https://artportalen.se/Sighting/132821594</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132821719</v>
+        <v>132821661</v>
       </c>
       <c r="B72" t="n">
         <v>99195</v>
@@ -8781,11 +8776,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>stjälkar/strån/skott</t>
@@ -8797,10 +8788,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>696709</v>
+        <v>696690</v>
       </c>
       <c r="R72" t="n">
-        <v>6643709</v>
+        <v>6643717</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8832,7 +8823,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8842,7 +8833,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8862,19 +8853,19 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821719</t>
+          <t>https://artportalen.se/Sighting/132821661</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132821892</v>
+        <v>132821719</v>
       </c>
       <c r="B73" t="n">
         <v>99195</v>
@@ -8904,7 +8895,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8918,10 +8909,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>696722</v>
+        <v>696709</v>
       </c>
       <c r="R73" t="n">
-        <v>6643684</v>
+        <v>6643709</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8953,7 +8944,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8963,7 +8954,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8989,13 +8980,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821892</t>
+          <t>https://artportalen.se/Sighting/132821719</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132822271</v>
+        <v>132821892</v>
       </c>
       <c r="B74" t="n">
         <v>99195</v>
@@ -9025,7 +9016,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9039,10 +9030,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>696774</v>
+        <v>696722</v>
       </c>
       <c r="R74" t="n">
-        <v>6643715</v>
+        <v>6643684</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9074,7 +9065,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9084,7 +9075,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9110,13 +9101,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132822271</t>
+          <t>https://artportalen.se/Sighting/132821892</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132822662</v>
+        <v>132822271</v>
       </c>
       <c r="B75" t="n">
         <v>99195</v>
@@ -9146,7 +9137,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9160,10 +9151,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>696811</v>
+        <v>696774</v>
       </c>
       <c r="R75" t="n">
-        <v>6643816</v>
+        <v>6643715</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9195,7 +9186,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9205,7 +9196,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9231,13 +9222,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132822662</t>
+          <t>https://artportalen.se/Sighting/132822271</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132822683</v>
+        <v>132822662</v>
       </c>
       <c r="B76" t="n">
         <v>99195</v>
@@ -9267,7 +9258,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9281,10 +9272,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>696803</v>
+        <v>696811</v>
       </c>
       <c r="R76" t="n">
-        <v>6643814</v>
+        <v>6643816</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9316,7 +9307,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9326,7 +9317,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9352,13 +9343,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132822683</t>
+          <t>https://artportalen.se/Sighting/132822662</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132822772</v>
+        <v>132822683</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -9388,7 +9379,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9402,10 +9393,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>696813</v>
+        <v>696803</v>
       </c>
       <c r="R77" t="n">
-        <v>6643818</v>
+        <v>6643814</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9437,7 +9428,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9447,7 +9438,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9467,19 +9458,19 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132822772</t>
+          <t>https://artportalen.se/Sighting/132822683</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132822866</v>
+        <v>132822772</v>
       </c>
       <c r="B78" t="n">
         <v>99195</v>
@@ -9509,7 +9500,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9523,10 +9514,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>696815</v>
+        <v>696813</v>
       </c>
       <c r="R78" t="n">
-        <v>6643822</v>
+        <v>6643818</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9558,7 +9549,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9568,7 +9559,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9588,19 +9579,19 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132822866</t>
+          <t>https://artportalen.se/Sighting/132822772</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132822951</v>
+        <v>132822866</v>
       </c>
       <c r="B79" t="n">
         <v>99195</v>
@@ -9630,7 +9621,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -9644,10 +9635,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>696846</v>
+        <v>696815</v>
       </c>
       <c r="R79" t="n">
-        <v>6643821</v>
+        <v>6643822</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9679,7 +9670,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9689,7 +9680,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9715,13 +9706,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132822951</t>
+          <t>https://artportalen.se/Sighting/132822866</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132823051</v>
+        <v>132822951</v>
       </c>
       <c r="B80" t="n">
         <v>99195</v>
@@ -9751,7 +9742,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>105</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9765,7 +9756,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>696853</v>
+        <v>696846</v>
       </c>
       <c r="R80" t="n">
         <v>6643821</v>
@@ -9800,7 +9791,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9810,7 +9801,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9836,13 +9827,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132823051</t>
+          <t>https://artportalen.se/Sighting/132822951</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132823172</v>
+        <v>132823051</v>
       </c>
       <c r="B81" t="n">
         <v>99195</v>
@@ -9872,7 +9863,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9886,10 +9877,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>696885</v>
+        <v>696853</v>
       </c>
       <c r="R81" t="n">
-        <v>6643816</v>
+        <v>6643821</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9921,7 +9912,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9931,7 +9922,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9957,13 +9948,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132823172</t>
+          <t>https://artportalen.se/Sighting/132823051</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132823255</v>
+        <v>132823172</v>
       </c>
       <c r="B82" t="n">
         <v>99195</v>
@@ -9993,7 +9984,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10007,10 +9998,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>696904</v>
+        <v>696885</v>
       </c>
       <c r="R82" t="n">
-        <v>6643781</v>
+        <v>6643816</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10042,7 +10033,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10052,7 +10043,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10078,13 +10069,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132823255</t>
+          <t>https://artportalen.se/Sighting/132823172</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132823493</v>
+        <v>132823255</v>
       </c>
       <c r="B83" t="n">
         <v>99195</v>
@@ -10114,7 +10105,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10128,10 +10119,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>696964</v>
+        <v>696904</v>
       </c>
       <c r="R83" t="n">
-        <v>6643823</v>
+        <v>6643781</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10163,7 +10154,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10173,7 +10164,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10199,13 +10190,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132823493</t>
+          <t>https://artportalen.se/Sighting/132823255</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132825468</v>
+        <v>132823493</v>
       </c>
       <c r="B84" t="n">
         <v>99195</v>
@@ -10235,7 +10226,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10249,10 +10240,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>696704</v>
+        <v>696964</v>
       </c>
       <c r="R84" t="n">
-        <v>6643630</v>
+        <v>6643823</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10284,7 +10275,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10294,7 +10285,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10320,13 +10311,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132825468</t>
+          <t>https://artportalen.se/Sighting/132823493</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132825569</v>
+        <v>132825468</v>
       </c>
       <c r="B85" t="n">
         <v>99195</v>
@@ -10356,7 +10347,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10370,7 +10361,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>696671</v>
+        <v>696704</v>
       </c>
       <c r="R85" t="n">
         <v>6643630</v>
@@ -10405,7 +10396,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10415,7 +10406,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10441,13 +10432,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132825569</t>
+          <t>https://artportalen.se/Sighting/132825468</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132826107</v>
+        <v>132825569</v>
       </c>
       <c r="B86" t="n">
         <v>99195</v>
@@ -10477,7 +10468,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10491,10 +10482,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>696530</v>
+        <v>696671</v>
       </c>
       <c r="R86" t="n">
-        <v>6643699</v>
+        <v>6643630</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10526,7 +10517,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10536,7 +10527,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10562,13 +10553,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132826107</t>
+          <t>https://artportalen.se/Sighting/132825569</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132830913</v>
+        <v>132826107</v>
       </c>
       <c r="B87" t="n">
         <v>99195</v>
@@ -10598,7 +10589,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10608,14 +10599,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>696702</v>
+        <v>696530</v>
       </c>
       <c r="R87" t="n">
-        <v>6643704</v>
+        <v>6643699</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10647,7 +10638,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10657,7 +10648,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10672,24 +10663,24 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830913</t>
+          <t>https://artportalen.se/Sighting/132826107</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132830915</v>
+        <v>132830913</v>
       </c>
       <c r="B88" t="n">
         <v>99195</v>
@@ -10719,7 +10710,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10733,10 +10724,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>696686</v>
+        <v>696702</v>
       </c>
       <c r="R88" t="n">
-        <v>6643680</v>
+        <v>6643704</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10768,7 +10759,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10778,7 +10769,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10804,13 +10795,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830915</t>
+          <t>https://artportalen.se/Sighting/132830913</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132830927</v>
+        <v>132830915</v>
       </c>
       <c r="B89" t="n">
         <v>99195</v>
@@ -10840,7 +10831,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -10850,14 +10841,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>696972</v>
+        <v>696686</v>
       </c>
       <c r="R89" t="n">
-        <v>6643904</v>
+        <v>6643680</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10889,7 +10880,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10899,7 +10890,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10925,13 +10916,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830927</t>
+          <t>https://artportalen.se/Sighting/132830915</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132830933</v>
+        <v>132830927</v>
       </c>
       <c r="B90" t="n">
         <v>99195</v>
@@ -10961,7 +10952,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -10975,10 +10966,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>696939</v>
+        <v>696972</v>
       </c>
       <c r="R90" t="n">
-        <v>6643882</v>
+        <v>6643904</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11010,7 +11001,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11020,7 +11011,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11046,13 +11037,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830933</t>
+          <t>https://artportalen.se/Sighting/132830927</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132830942</v>
+        <v>132830933</v>
       </c>
       <c r="B91" t="n">
         <v>99195</v>
@@ -11082,7 +11073,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11092,14 +11083,14 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>696776</v>
+        <v>696939</v>
       </c>
       <c r="R91" t="n">
-        <v>6643778</v>
+        <v>6643882</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11131,7 +11122,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11141,7 +11132,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11167,13 +11158,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830942</t>
+          <t>https://artportalen.se/Sighting/132830933</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132830946</v>
+        <v>132830942</v>
       </c>
       <c r="B92" t="n">
         <v>99195</v>
@@ -11203,7 +11194,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11217,10 +11208,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>696782</v>
+        <v>696776</v>
       </c>
       <c r="R92" t="n">
-        <v>6643729</v>
+        <v>6643778</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11252,7 +11243,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11262,7 +11253,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11288,13 +11279,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830946</t>
+          <t>https://artportalen.se/Sighting/132830942</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132830956</v>
+        <v>132830946</v>
       </c>
       <c r="B93" t="n">
         <v>99195</v>
@@ -11324,7 +11315,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11338,10 +11329,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>696730</v>
+        <v>696782</v>
       </c>
       <c r="R93" t="n">
-        <v>6643665</v>
+        <v>6643729</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11373,7 +11364,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11383,7 +11374,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11409,13 +11400,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830956</t>
+          <t>https://artportalen.se/Sighting/132830946</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132830974</v>
+        <v>132830956</v>
       </c>
       <c r="B94" t="n">
         <v>99195</v>
@@ -11445,7 +11436,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11459,10 +11450,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>696678</v>
+        <v>696730</v>
       </c>
       <c r="R94" t="n">
-        <v>6643668</v>
+        <v>6643665</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11494,7 +11485,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11504,12 +11495,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>08:54</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11535,13 +11521,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830974</t>
+          <t>https://artportalen.se/Sighting/132830956</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132830979</v>
+        <v>132830974</v>
       </c>
       <c r="B95" t="n">
         <v>99195</v>
@@ -11571,7 +11557,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11585,10 +11571,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>696663</v>
+        <v>696678</v>
       </c>
       <c r="R95" t="n">
-        <v>6643658</v>
+        <v>6643668</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11620,7 +11606,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11630,7 +11616,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11656,13 +11647,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830979</t>
+          <t>https://artportalen.se/Sighting/132830974</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132830985</v>
+        <v>132830979</v>
       </c>
       <c r="B96" t="n">
         <v>99195</v>
@@ -11692,7 +11683,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -11706,10 +11697,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>696679</v>
+        <v>696663</v>
       </c>
       <c r="R96" t="n">
-        <v>6643623</v>
+        <v>6643658</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11741,7 +11732,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11751,12 +11742,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>1 vinterståndare</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11782,13 +11768,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830985</t>
+          <t>https://artportalen.se/Sighting/132830979</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133089120</v>
+        <v>132830985</v>
       </c>
       <c r="B97" t="n">
         <v>99195</v>
@@ -11818,7 +11804,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11826,23 +11812,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Eklund V om 2 (*knärot* /stjälk/), Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>696529</v>
+        <v>696679</v>
       </c>
       <c r="R97" t="n">
-        <v>6643700</v>
+        <v>6643623</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11867,59 +11846,64 @@
           <t>Edsbro</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>AB-Nor-1962</t>
-        </is>
-      </c>
       <c r="Y97" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1 vinterståndare</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133089120</t>
+          <t>https://artportalen.se/Sighting/132830985</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137373636</v>
+        <v>133089120</v>
       </c>
       <c r="B98" t="n">
-        <v>99430</v>
+        <v>99195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11944,20 +11928,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Eklund V om 2 (*knärot* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>696753</v>
+        <v>696529</v>
       </c>
       <c r="R98" t="n">
-        <v>6643786</v>
+        <v>6643700</v>
       </c>
       <c r="S98" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11979,24 +11979,19 @@
           <t>Edsbro</t>
         </is>
       </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>AB-Nor-1962</t>
+        </is>
+      </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12005,85 +12000,76 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373636</t>
+          <t>https://artportalen.se/Sighting/133089120</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>122318555</v>
+        <v>137373636</v>
       </c>
       <c r="B99" t="n">
-        <v>106244</v>
+        <v>99431</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>696752</v>
+        <v>696753</v>
       </c>
       <c r="R99" t="n">
-        <v>6643853</v>
+        <v>6643786</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12107,12 +12093,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12127,27 +12123,27 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122318555</t>
+          <t>https://artportalen.se/Sighting/137373636</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132821927</v>
+        <v>122318555</v>
       </c>
       <c r="B100" t="n">
-        <v>106324</v>
+        <v>106244</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12172,17 +12168,31 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Barrnaturskog NV Eklund , Eklund, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>696722</v>
+        <v>696752</v>
       </c>
       <c r="R100" t="n">
-        <v>6643677</v>
+        <v>6643853</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12209,22 +12219,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>09:23</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>09:23</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12239,65 +12239,65 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132821927</t>
+          <t>https://artportalen.se/Sighting/122318555</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137373629</v>
+        <v>132821927</v>
       </c>
       <c r="B101" t="n">
-        <v>102562</v>
+        <v>106324</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>696640</v>
+        <v>696722</v>
       </c>
       <c r="R101" t="n">
-        <v>6643744</v>
+        <v>6643677</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12321,22 +12321,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12351,68 +12351,65 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373629</t>
+          <t>https://artportalen.se/Sighting/132821927</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>55544918</v>
+        <v>137373629</v>
       </c>
       <c r="B102" t="n">
-        <v>101326</v>
+        <v>102563</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ekllund, SV om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>696728</v>
+        <v>696640</v>
       </c>
       <c r="R102" t="n">
-        <v>6643586</v>
+        <v>6643744</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12436,12 +12433,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12456,27 +12463,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55544918</t>
+          <t>https://artportalen.se/Sighting/137373629</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132830923</v>
+        <v>55544918</v>
       </c>
       <c r="B103" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12502,19 +12509,22 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Ekllund, SV om, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>697051</v>
+        <v>696728</v>
       </c>
       <c r="R103" t="n">
-        <v>6643938</v>
+        <v>6643586</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12538,22 +12548,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>10:20</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12568,24 +12568,24 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830923</t>
+          <t>https://artportalen.se/Sighting/55544918</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>132830925</v>
+        <v>132830923</v>
       </c>
       <c r="B104" t="n">
         <v>101403</v>
@@ -12620,10 +12620,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>697028</v>
+        <v>697051</v>
       </c>
       <c r="R104" t="n">
-        <v>6643921</v>
+        <v>6643938</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12691,13 +12691,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830925</t>
+          <t>https://artportalen.se/Sighting/132830923</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132830929</v>
+        <v>132830925</v>
       </c>
       <c r="B105" t="n">
         <v>101403</v>
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>697012</v>
+        <v>697028</v>
       </c>
       <c r="R105" t="n">
-        <v>6643911</v>
+        <v>6643921</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12803,13 +12803,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830929</t>
+          <t>https://artportalen.se/Sighting/132830925</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132830930</v>
+        <v>132830929</v>
       </c>
       <c r="B106" t="n">
         <v>101403</v>
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>697027</v>
+        <v>697012</v>
       </c>
       <c r="R106" t="n">
-        <v>6643874</v>
+        <v>6643911</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12879,7 +12879,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12915,13 +12915,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830930</t>
+          <t>https://artportalen.se/Sighting/132830929</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132830932</v>
+        <v>132830930</v>
       </c>
       <c r="B107" t="n">
         <v>101403</v>
@@ -12956,10 +12956,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>696970</v>
+        <v>697027</v>
       </c>
       <c r="R107" t="n">
-        <v>6643862</v>
+        <v>6643874</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13027,13 +13027,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830932</t>
+          <t>https://artportalen.se/Sighting/132830930</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132830934</v>
+        <v>132830932</v>
       </c>
       <c r="B108" t="n">
         <v>101403</v>
@@ -13068,10 +13068,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>696926</v>
+        <v>696970</v>
       </c>
       <c r="R108" t="n">
-        <v>6643877</v>
+        <v>6643862</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13103,7 +13103,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13139,13 +13139,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830934</t>
+          <t>https://artportalen.se/Sighting/132830932</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>132830935</v>
+        <v>132830934</v>
       </c>
       <c r="B109" t="n">
         <v>101403</v>
@@ -13180,10 +13180,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>696897</v>
+        <v>696926</v>
       </c>
       <c r="R109" t="n">
-        <v>6643810</v>
+        <v>6643877</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13251,13 +13251,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830935</t>
+          <t>https://artportalen.se/Sighting/132830934</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132830937</v>
+        <v>132830935</v>
       </c>
       <c r="B110" t="n">
         <v>101403</v>
@@ -13288,14 +13288,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>696837</v>
+        <v>696897</v>
       </c>
       <c r="R110" t="n">
-        <v>6643803</v>
+        <v>6643810</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13337,7 +13337,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13363,13 +13363,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830937</t>
+          <t>https://artportalen.se/Sighting/132830935</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132830940</v>
+        <v>132830937</v>
       </c>
       <c r="B111" t="n">
         <v>101403</v>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>696814</v>
+        <v>696837</v>
       </c>
       <c r="R111" t="n">
-        <v>6643811</v>
+        <v>6643803</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13475,13 +13475,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830940</t>
+          <t>https://artportalen.se/Sighting/132830937</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132830941</v>
+        <v>132830940</v>
       </c>
       <c r="B112" t="n">
         <v>101403</v>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>696790</v>
+        <v>696814</v>
       </c>
       <c r="R112" t="n">
-        <v>6643780</v>
+        <v>6643811</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13551,7 +13551,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13587,13 +13587,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830941</t>
+          <t>https://artportalen.se/Sighting/132830940</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132830943</v>
+        <v>132830941</v>
       </c>
       <c r="B113" t="n">
         <v>101403</v>
@@ -13628,10 +13628,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>696778</v>
+        <v>696790</v>
       </c>
       <c r="R113" t="n">
-        <v>6643770</v>
+        <v>6643780</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13699,13 +13699,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830943</t>
+          <t>https://artportalen.se/Sighting/132830941</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>132830949</v>
+        <v>132830943</v>
       </c>
       <c r="B114" t="n">
         <v>101403</v>
@@ -13740,10 +13740,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>696758</v>
+        <v>696778</v>
       </c>
       <c r="R114" t="n">
-        <v>6643677</v>
+        <v>6643770</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13811,13 +13811,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830949</t>
+          <t>https://artportalen.se/Sighting/132830943</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>132830954</v>
+        <v>132830949</v>
       </c>
       <c r="B115" t="n">
         <v>101403</v>
@@ -13852,10 +13852,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>696732</v>
+        <v>696758</v>
       </c>
       <c r="R115" t="n">
-        <v>6643642</v>
+        <v>6643677</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13887,7 +13887,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13897,7 +13897,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13923,13 +13923,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830954</t>
+          <t>https://artportalen.se/Sighting/132830949</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132830957</v>
+        <v>132830954</v>
       </c>
       <c r="B116" t="n">
         <v>101403</v>
@@ -13964,10 +13964,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>696757</v>
+        <v>696732</v>
       </c>
       <c r="R116" t="n">
-        <v>6643672</v>
+        <v>6643642</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13999,7 +13999,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14009,7 +14009,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14035,13 +14035,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830957</t>
+          <t>https://artportalen.se/Sighting/132830954</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132830960</v>
+        <v>132830957</v>
       </c>
       <c r="B117" t="n">
         <v>101403</v>
@@ -14076,10 +14076,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>696741</v>
+        <v>696757</v>
       </c>
       <c r="R117" t="n">
-        <v>6643703</v>
+        <v>6643672</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14121,7 +14121,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14147,13 +14147,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830960</t>
+          <t>https://artportalen.se/Sighting/132830957</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>132830962</v>
+        <v>132830960</v>
       </c>
       <c r="B118" t="n">
         <v>101403</v>
@@ -14188,10 +14188,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>696727</v>
+        <v>696741</v>
       </c>
       <c r="R118" t="n">
-        <v>6643708</v>
+        <v>6643703</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14259,13 +14259,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830962</t>
+          <t>https://artportalen.se/Sighting/132830960</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132830970</v>
+        <v>132830962</v>
       </c>
       <c r="B119" t="n">
         <v>101403</v>
@@ -14300,10 +14300,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>696614</v>
+        <v>696727</v>
       </c>
       <c r="R119" t="n">
-        <v>6643745</v>
+        <v>6643708</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14345,7 +14345,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14371,13 +14371,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830970</t>
+          <t>https://artportalen.se/Sighting/132830962</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>132830976</v>
+        <v>132830970</v>
       </c>
       <c r="B120" t="n">
         <v>101403</v>
@@ -14412,10 +14412,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>696677</v>
+        <v>696614</v>
       </c>
       <c r="R120" t="n">
-        <v>6643661</v>
+        <v>6643745</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14483,16 +14483,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830976</t>
+          <t>https://artportalen.se/Sighting/132830970</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>132830922</v>
+        <v>132830976</v>
       </c>
       <c r="B121" t="n">
-        <v>99001</v>
+        <v>101403</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14500,34 +14500,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Fansjön, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>697038</v>
+        <v>696677</v>
       </c>
       <c r="R121" t="n">
-        <v>6643950</v>
+        <v>6643661</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14569,7 +14569,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14595,57 +14595,54 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830922</t>
+          <t>https://artportalen.se/Sighting/132830976</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>55545583</v>
+        <v>132830922</v>
       </c>
       <c r="B122" t="n">
-        <v>103403</v>
+        <v>99001</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>223246</v>
+        <v>223049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Eklund, NO om, Upl</t>
+          <t>Fansjön, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>697082</v>
+        <v>697038</v>
       </c>
       <c r="R122" t="n">
-        <v>6643889</v>
+        <v>6643950</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14669,17 +14666,22 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>En frisk alm ca 70 år gammal. Gammal barrblandskog på delvis kalkhaltig mark.</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14694,65 +14696,68 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545583</t>
+          <t>https://artportalen.se/Sighting/132830922</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>137373638</v>
+        <v>55545583</v>
       </c>
       <c r="B123" t="n">
-        <v>87566</v>
+        <v>103403</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>249228</v>
+        <v>223246</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Eklund, Upl</t>
+          <t>Eklund, NO om, Upl</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>696775</v>
+        <v>697082</v>
       </c>
       <c r="R123" t="n">
-        <v>6643780</v>
+        <v>6643889</v>
       </c>
       <c r="S123" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14776,22 +14781,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>En frisk alm ca 70 år gammal. Gammal barrblandskog på delvis kalkhaltig mark.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14806,76 +14806,65 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137373638</t>
+          <t>https://artportalen.se/Sighting/55545583</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>137373657</v>
+        <v>137373638</v>
       </c>
       <c r="B124" t="n">
-        <v>87472</v>
+        <v>87567</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6038612</v>
+        <v>249228</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Koboltspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cortinarius cobaltinus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>697021</v>
+        <v>696775</v>
       </c>
       <c r="R124" t="n">
-        <v>6643905</v>
+        <v>6643780</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14904,7 +14893,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14914,21 +14903,15 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Jordgubbssaft med K på hatten, tuschpennerosa på basalmycel. I mossa i kalkbarrskog under grov gran. Ska sekvenseras.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF124" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14945,6 +14928,135 @@
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373638</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>137373657</v>
+      </c>
+      <c r="B125" t="n">
+        <v>87473</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6038612</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Koboltspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius cobaltinus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>697021</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6643905</v>
+      </c>
+      <c r="S125" t="n">
+        <v>9</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Jordgubbssaft med K på hatten, tuschpennerosa på basalmycel. I mossa i kalkbarrskog under grov gran. Ska sekvenseras.</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137373657</t>
         </is>
@@ -15075,6 +15187,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>137373634</v>
       </c>
       <c r="B4" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137373635</v>
       </c>
       <c r="B5" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137373627</v>
       </c>
       <c r="B14" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>137400918</v>
       </c>
       <c r="B15" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>137373637</v>
       </c>
       <c r="B16" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>137373642</v>
       </c>
       <c r="B17" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137373645</v>
       </c>
       <c r="B23" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>137373633</v>
       </c>
       <c r="B27" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137373639</v>
       </c>
       <c r="B28" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>137373643</v>
       </c>
       <c r="B29" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>137373649</v>
       </c>
       <c r="B30" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137373650</v>
       </c>
       <c r="B31" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>137373652</v>
       </c>
       <c r="B32" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137373655</v>
       </c>
       <c r="B33" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137373631</v>
       </c>
       <c r="B34" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>137373630</v>
       </c>
       <c r="B47" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>137373653</v>
       </c>
       <c r="B48" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>137373636</v>
       </c>
       <c r="B99" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137373629</v>
       </c>
       <c r="B102" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>137373638</v>
       </c>
       <c r="B124" t="n">
-        <v>87567</v>
+        <v>87570</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>137373657</v>
       </c>
       <c r="B125" t="n">
-        <v>87473</v>
+        <v>87476</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/A 17645-2026 artfynd.xlsx
+++ b/artfynd/A 17645-2026 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>137373634</v>
       </c>
       <c r="B4" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>137373635</v>
       </c>
       <c r="B5" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>137373627</v>
       </c>
       <c r="B14" t="n">
-        <v>87622</v>
+        <v>87626</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>137400918</v>
       </c>
       <c r="B15" t="n">
-        <v>87622</v>
+        <v>87626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>137373637</v>
       </c>
       <c r="B16" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>137373642</v>
       </c>
       <c r="B17" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>137373645</v>
       </c>
       <c r="B23" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>137373633</v>
       </c>
       <c r="B27" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>137373639</v>
       </c>
       <c r="B28" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>137373643</v>
       </c>
       <c r="B29" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>137373649</v>
       </c>
       <c r="B30" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>137373650</v>
       </c>
       <c r="B31" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>137373652</v>
       </c>
       <c r="B32" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137373655</v>
       </c>
       <c r="B33" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137373631</v>
       </c>
       <c r="B34" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>137373630</v>
       </c>
       <c r="B47" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5901,7 +5901,7 @@
         <v>137373653</v>
       </c>
       <c r="B48" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>137373636</v>
       </c>
       <c r="B99" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137373629</v>
       </c>
       <c r="B102" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>137373638</v>
       </c>
       <c r="B124" t="n">
-        <v>87570</v>
+        <v>87574</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>137373657</v>
       </c>
       <c r="B125" t="n">
-        <v>87476</v>
+        <v>87480</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
